--- a/学生监护人，政治面貌.xlsx
+++ b/学生监护人，政治面貌.xlsx
@@ -1236,11 +1236,7 @@
           <t>362525198407022426</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>共产主义青年团团员</t>
-        </is>
-      </c>
+      <c r="I4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1408,11 +1404,7 @@
           <t>362525198510262719</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>共产主义青年团团员</t>
-        </is>
-      </c>
+      <c r="I8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1954,11 +1946,7 @@
           <t>362525198912134218</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>共产主义青年团团员</t>
-        </is>
-      </c>
+      <c r="I21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2042,11 +2030,7 @@
           <t>362525198411253913</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>共产主义青年团团员</t>
-        </is>
-      </c>
+      <c r="I23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2886,11 +2870,7 @@
           <t>362525198308140910</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>共产主义青年团团员</t>
-        </is>
-      </c>
+      <c r="I43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -2974,11 +2954,7 @@
           <t>362502197811180216</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>共产主义青年团团员</t>
-        </is>
-      </c>
+      <c r="I45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
